--- a/dcf/ENB.xlsx
+++ b/dcf/ENB.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1139,25 +1139,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.03926243689458903</v>
+        <v>0.03933952159998694</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.04426243689458902</v>
+        <v>0.04433952159998693</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.04926243689458903</v>
+        <v>0.04933952159998694</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.05426243689458903</v>
+        <v>0.05433952159998694</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.05926243689458902</v>
+        <v>0.05933952159998693</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.06426243689458902</v>
+        <v>0.06433952159998693</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.06926243689458902</v>
+        <v>0.06933952159998694</v>
       </c>
     </row>
     <row r="5">
@@ -1165,25 +1165,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>8.796273063510139</v>
+        <v>8.758210819816741</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>6.388276219438334</v>
+        <v>6.352101937586386</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>4.099407584247743</v>
+        <v>4.065017990068912</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>1.923166529052538</v>
+        <v>1.890464483972582</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>-0.1465622747517611</v>
+        <v>-0.1776681660067833</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>-2.115533433909648</v>
+        <v>-2.145129188792366</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>-3.989163735510336</v>
+        <v>-4.01733033426544</v>
       </c>
     </row>
     <row r="6">
@@ -1191,25 +1191,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>13.55898906644529</v>
+        <v>13.51739563736422</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>10.9278013733004</v>
+        <v>10.88827749349754</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>8.427193148198256</v>
+        <v>8.389625404245431</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>6.050025806311052</v>
+        <v>6.014307530845036</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>3.789584387170557</v>
+        <v>3.755615227199502</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>1.639550508342615</v>
+        <v>1.607236023079249</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>-0.4060228351900438</v>
+        <v>-0.4367715491159716</v>
       </c>
     </row>
     <row r="7">
@@ -1217,25 +1217,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>18.32170506938046</v>
+        <v>18.2765804549117</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>15.46732652716248</v>
+        <v>15.42445304940869</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>12.75497871214877</v>
+        <v>12.71423281842195</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>10.17688508356957</v>
+        <v>10.1381505777175</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>7.725731049092887</v>
+        <v>7.688898620405797</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>5.394634450594898</v>
+        <v>5.359601234950862</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>3.177118065130248</v>
+        <v>3.143787236033487</v>
       </c>
     </row>
     <row r="8">
@@ -1243,25 +1243,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>23.08442107231561</v>
+        <v>23.03576527245919</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>20.00685168102455</v>
+        <v>19.96062860531985</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>17.08276427609928</v>
+        <v>17.03884023259847</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>14.3037443608281</v>
+        <v>14.26199362458995</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>11.6618777110152</v>
+        <v>11.62218201361209</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>9.149718392847161</v>
+        <v>9.111966446822466</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>6.76025896545053</v>
+        <v>6.724346021182945</v>
       </c>
     </row>
     <row r="9">
@@ -1269,25 +1269,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>27.84713707525077</v>
+        <v>27.79495009000667</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>24.54637683488662</v>
+        <v>24.496804161231</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>21.41054984004979</v>
+        <v>21.36344764677496</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>18.43060363808662</v>
+        <v>18.38583667146242</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>15.59802437293752</v>
+        <v>15.55546540681838</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>12.90480233509944</v>
+        <v>12.86433165869407</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>10.34339986577081</v>
+        <v>10.3049048063324</v>
       </c>
     </row>
     <row r="10">
@@ -1295,25 +1295,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>32.60985307818594</v>
+        <v>32.55413490755416</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>29.08590198874868</v>
+        <v>29.03297971714216</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>25.7383354040003</v>
+        <v>25.68805506095148</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>22.55746291534513</v>
+        <v>22.50967971833487</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>19.53417103485985</v>
+        <v>19.48874880002467</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>16.65988627735172</v>
+        <v>16.61669687056568</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>13.9265407660911</v>
+        <v>13.88546359148187</v>
       </c>
     </row>
     <row r="11">
@@ -1321,25 +1321,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>37.37256908112109</v>
+        <v>37.31331972510162</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>33.62542714261075</v>
+        <v>33.5691552730533</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>30.06612096795081</v>
+        <v>30.012662475128</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>26.68432219260365</v>
+        <v>26.63352276520732</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>23.47031769678216</v>
+        <v>23.42203219323096</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>20.41497021960399</v>
+        <v>20.36906208243728</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>17.50968166641138</v>
+        <v>17.46602237663132</v>
       </c>
     </row>
     <row r="13">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>54.08000183105469</v>
+        <v>54.45999908447266</v>
       </c>
     </row>
     <row r="14">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.05426243689458903</v>
+        <v>0.05433952159998694</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.593516114432356</v>
+        <v>0.5932233008045174</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24508,7 +24508,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>54.08000183105469</v>
+        <v>54.45999908447266</v>
       </c>
     </row>
     <row r="49">
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>14.3037443608281</v>
+        <v>14.26199362458995</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>45.3982188827625</v>
+        <v>45.33511396381343</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>-8.102741675975505</v>
+        <v>-8.12929168680814</v>
       </c>
     </row>
     <row r="59">
